--- a/Analysis/04_Robust_Core_and_Policy/5_pareto_and_balanced_scores.xlsx
+++ b/Analysis/04_Robust_Core_and_Policy/5_pareto_and_balanced_scores.xlsx
@@ -480,7 +480,7 @@
         <v>0.9838709677419355</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9193548387096774</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -489,13 +489,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9510659992132624</v>
+        <v>0.9593724101911646</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9193548387096774</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9352104189614698</v>
+        <v>0.9474281405794532</v>
       </c>
       <c r="I2" t="n">
         <v>0.5149786364148489</v>
@@ -514,7 +514,7 @@
         <v>0.8064516129032258</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0.9838709677419355</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -523,13 +523,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8980265101338745</v>
+        <v>0.8907549207409081</v>
       </c>
       <c r="G3" t="n">
         <v>0.8064516129032258</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8522390615185501</v>
+        <v>0.8486032668220669</v>
       </c>
       <c r="I3" t="n">
         <v>0.5149786364148489</v>
@@ -575,29 +575,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sec30</t>
+          <t>sec1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.2741935483870968</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9516129032258065</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8583312706871014</v>
+        <v>0.5236349380886428</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.2741935483870968</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8162624095370991</v>
+        <v>0.3989142432378698</v>
       </c>
       <c r="I5" t="n">
         <v>0.5149786364148489</v>
@@ -609,14 +609,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sec43</t>
+          <t>sec30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9032258064516129</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6935483870967742</v>
+        <v>0.9516129032258065</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
@@ -625,13 +625,13 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7914738158958257</v>
+        <v>0.8583312706871014</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6935483870967742</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7425111014963</v>
+        <v>0.8162624095370991</v>
       </c>
       <c r="I6" t="n">
         <v>0.5149786364148489</v>
@@ -643,14 +643,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sec41</t>
+          <t>sec43</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9193548387096774</v>
+        <v>0.9032258064516129</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5645161290322581</v>
+        <v>0.6935483870967742</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -659,13 +659,13 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7204100462621708</v>
+        <v>0.7914738158958257</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5645161290322581</v>
+        <v>0.6935483870967742</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6424630876472144</v>
+        <v>0.7425111014963</v>
       </c>
       <c r="I7" t="n">
         <v>0.5149786364148489</v>
@@ -677,14 +677,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sec36</t>
+          <t>sec41</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.9193548387096774</v>
       </c>
       <c r="C8" t="n">
-        <v>0.967741935483871</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -693,13 +693,13 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6246747332592607</v>
+        <v>0.7100438936469399</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5139502698554368</v>
+        <v>0.6292154952105666</v>
       </c>
       <c r="I8" t="n">
         <v>0.5149786364148489</v>
@@ -711,14 +711,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sec34</t>
+          <t>sec36</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.4032258064516129</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3387096774193548</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -727,13 +727,13 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5629009150521015</v>
+        <v>0.6246747332592607</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3387096774193548</v>
+        <v>0.4032258064516129</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4508052962357282</v>
+        <v>0.5139502698554368</v>
       </c>
       <c r="I9" t="n">
         <v>0.5149786364148489</v>
@@ -745,14 +745,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sec1</t>
+          <t>sec34</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2741935483870968</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.3387096774193548</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
@@ -761,13 +761,13 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5193949092936974</v>
+        <v>0.5629009150521015</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2741935483870968</v>
+        <v>0.3387096774193548</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3967942288403971</v>
+        <v>0.4508052962357282</v>
       </c>
       <c r="I10" t="n">
         <v>0.5149786364148489</v>
@@ -820,7 +820,7 @@
         <v>0.6935483870967742</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.9193548387096774</v>
       </c>
       <c r="D12" t="n">
         <v>3</v>
@@ -829,13 +829,13 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8054832896247596</v>
+        <v>0.7985092770636493</v>
       </c>
       <c r="G12" t="n">
         <v>0.6935483870967742</v>
       </c>
       <c r="H12" t="n">
-        <v>0.749515838360767</v>
+        <v>0.7460288320802118</v>
       </c>
       <c r="I12" t="n">
         <v>0.5149786364148489</v>
@@ -956,7 +956,7 @@
         <v>0.8709677419354839</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3548387096774194</v>
+        <v>0.3709677419354839</v>
       </c>
       <c r="D16" t="n">
         <v>3</v>
@@ -965,13 +965,13 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.555925417406906</v>
+        <v>0.5684196834421321</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3548387096774194</v>
+        <v>0.3709677419354839</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4553820635421627</v>
+        <v>0.469693712688808</v>
       </c>
       <c r="I16" t="n">
         <v>0.5149786364148489</v>
@@ -1024,7 +1024,7 @@
         <v>0.9516129032258065</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="D18" t="n">
         <v>3</v>
@@ -1033,13 +1033,13 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1238894475462679</v>
+        <v>0.1752061369548422</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0700092399021662</v>
+        <v>0.1037321007354856</v>
       </c>
       <c r="I18" t="n">
         <v>0.5149786364148489</v>
@@ -1160,7 +1160,7 @@
         <v>0.8387096774193549</v>
       </c>
       <c r="C22" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.01612903225806452</v>
       </c>
       <c r="D22" t="n">
         <v>4</v>
@@ -1169,13 +1169,13 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1644845004384769</v>
+        <v>0.1163081056601287</v>
       </c>
       <c r="G22" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.01612903225806452</v>
       </c>
       <c r="H22" t="n">
-        <v>0.09837128247730298</v>
+        <v>0.0662185689590966</v>
       </c>
       <c r="I22" t="n">
         <v>0.5149786364148489</v>
@@ -1228,7 +1228,7 @@
         <v>0.4516129032258064</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8225806451612904</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="D24" t="n">
         <v>5</v>
@@ -1237,13 +1237,13 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6094981815384253</v>
+        <v>0.6154446460754488</v>
       </c>
       <c r="G24" t="n">
         <v>0.4516129032258064</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5305555423821159</v>
+        <v>0.5335287746506276</v>
       </c>
       <c r="I24" t="n">
         <v>0.5149786364148489</v>
@@ -1289,14 +1289,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sec2</t>
+          <t>sec6</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2903225806451613</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.8709677419354839</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
@@ -1305,13 +1305,13 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4934535013154308</v>
+        <v>0.4434750672537909</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2903225806451613</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3918880409802961</v>
+        <v>0.3346407594333471</v>
       </c>
       <c r="I26" t="n">
         <v>0.5149786364148489</v>
@@ -1323,14 +1323,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sec6</t>
+          <t>sec47</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.1451612903225807</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8548387096774194</v>
+        <v>0.8870967741935484</v>
       </c>
       <c r="D27" t="n">
         <v>5</v>
@@ -1339,13 +1339,13 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4393496281250399</v>
+        <v>0.3588483138917257</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.1451612903225807</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3325780398689716</v>
+        <v>0.2520048021071531</v>
       </c>
       <c r="I27" t="n">
         <v>0.5149786364148489</v>
@@ -1357,14 +1357,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sec61</t>
+          <t>sec14</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2096774193548387</v>
+        <v>0.7419354838709677</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.08064516129032258</v>
       </c>
       <c r="D28" t="n">
         <v>5</v>
@@ -1373,13 +1373,13 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.427343267725541</v>
+        <v>0.2446088852919855</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2096774193548387</v>
+        <v>0.08064516129032258</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3185103435401899</v>
+        <v>0.1626270232911541</v>
       </c>
       <c r="I28" t="n">
         <v>0.5149786364148489</v>
@@ -1391,29 +1391,29 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>sec47</t>
+          <t>sec59</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1451612903225807</v>
+        <v>0.4677419354838709</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8870967741935484</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3588483138917257</v>
+        <v>0.5629009150521015</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1451612903225807</v>
+        <v>0.4677419354838709</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2520048021071531</v>
+        <v>0.5153214252679862</v>
       </c>
       <c r="I29" t="n">
         <v>0.5149786364148489</v>
@@ -1425,29 +1425,29 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sec14</t>
+          <t>sec42</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="C30" t="n">
-        <v>0.08064516129032258</v>
+        <v>0.532258064516129</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2446088852919855</v>
+        <v>0.5074881523403959</v>
       </c>
       <c r="G30" t="n">
-        <v>0.08064516129032258</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1626270232911541</v>
+        <v>0.4956795600411657</v>
       </c>
       <c r="I30" t="n">
         <v>0.5149786364148489</v>
@@ -1459,14 +1459,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sec59</t>
+          <t>sec7</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4677419354838709</v>
+        <v>0.5967741935483871</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="D31" t="n">
         <v>6</v>
@@ -1475,13 +1475,13 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5629009150521015</v>
+        <v>0.5002600780409944</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4677419354838709</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5153214252679862</v>
+        <v>0.4598074583753359</v>
       </c>
       <c r="I31" t="n">
         <v>0.5149786364148489</v>
@@ -1493,14 +1493,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sec42</t>
+          <t>sec2</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="C32" t="n">
-        <v>0.532258064516129</v>
+        <v>0.8225806451612904</v>
       </c>
       <c r="D32" t="n">
         <v>6</v>
@@ -1509,13 +1509,13 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5074881523403959</v>
+        <v>0.4886857228239715</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4956795600411657</v>
+        <v>0.3895041517345664</v>
       </c>
       <c r="I32" t="n">
         <v>0.5149786364148489</v>
@@ -1527,14 +1527,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>sec7</t>
+          <t>sec8</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5967741935483871</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.3064516129032258</v>
       </c>
       <c r="D33" t="n">
         <v>6</v>
@@ -1543,13 +1543,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4905453653466306</v>
+        <v>0.4446467339383943</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.3064516129032258</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4468855858991218</v>
+        <v>0.3755491734208101</v>
       </c>
       <c r="I33" t="n">
         <v>0.5149786364148489</v>
@@ -1561,14 +1561,14 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sec8</t>
+          <t>sec4</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.6612903225806451</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3064516129032258</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="D34" t="n">
         <v>6</v>
@@ -1577,13 +1577,13 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4446467339383943</v>
+        <v>0.4131047895117967</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3064516129032258</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3755491734208101</v>
+        <v>0.3355846528204145</v>
       </c>
       <c r="I34" t="n">
         <v>0.5149786364148489</v>
@@ -1595,14 +1595,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sec25</t>
+          <t>sec61</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.2580645161290323</v>
+        <v>0.2096774193548387</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.8548387096774194</v>
       </c>
       <c r="D35" t="n">
         <v>6</v>
@@ -1611,13 +1611,13 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4469808535661619</v>
+        <v>0.4233678951098931</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2580645161290323</v>
+        <v>0.2096774193548387</v>
       </c>
       <c r="H35" t="n">
-        <v>0.3525226848475971</v>
+        <v>0.3165226572323659</v>
       </c>
       <c r="I35" t="n">
         <v>0.5149786364148489</v>
@@ -1629,29 +1629,29 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>sec4</t>
+          <t>sec28</t>
         </is>
       </c>
       <c r="B36" t="n">
+        <v>0.3709677419354839</v>
+      </c>
+      <c r="C36" t="n">
         <v>0.6612903225806451</v>
       </c>
-      <c r="C36" t="n">
-        <v>0.2258064516129032</v>
-      </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3864241467971271</v>
+        <v>0.4952952429930351</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.3709677419354839</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3061152992050151</v>
+        <v>0.4331314924642595</v>
       </c>
       <c r="I36" t="n">
         <v>0.5149786364148489</v>
@@ -1663,29 +1663,29 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>sec57</t>
+          <t>sec26</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.08064516129032258</v>
+        <v>0.5806451612903226</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8064516129032258</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2550223919490628</v>
+        <v>0.4740947889257764</v>
       </c>
       <c r="G37" t="n">
-        <v>0.08064516129032258</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1678337766196927</v>
+        <v>0.4305957815596624</v>
       </c>
       <c r="I37" t="n">
         <v>0.5149786364148489</v>
@@ -1697,14 +1697,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>sec28</t>
+          <t>sec32</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.3709677419354839</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="C38" t="n">
-        <v>0.6612903225806451</v>
+        <v>0.5</v>
       </c>
       <c r="D38" t="n">
         <v>7</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4952952429930351</v>
+        <v>0.4399413450640599</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3709677419354839</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4331314924642595</v>
+        <v>0.4135190596288041</v>
       </c>
       <c r="I38" t="n">
         <v>0.5149786364148489</v>
@@ -1731,14 +1731,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>sec26</t>
+          <t>sec25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5806451612903226</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="D39" t="n">
         <v>7</v>
@@ -1747,13 +1747,13 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4740947889257764</v>
+        <v>0.4469808535661619</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4305957815596624</v>
+        <v>0.3525226848475971</v>
       </c>
       <c r="I39" t="n">
         <v>0.5149786364148489</v>
@@ -1765,14 +1765,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>sec32</t>
+          <t>sec13</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.6290322580645161</v>
       </c>
       <c r="C40" t="n">
-        <v>0.5</v>
+        <v>0.1451612903225807</v>
       </c>
       <c r="D40" t="n">
         <v>7</v>
@@ -1781,13 +1781,13 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4399413450640599</v>
+        <v>0.3021773225031483</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.1451612903225807</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4135190596288041</v>
+        <v>0.2236693064128645</v>
       </c>
       <c r="I40" t="n">
         <v>0.5149786364148489</v>
@@ -1799,14 +1799,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>sec13</t>
+          <t>sec57</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6290322580645161</v>
+        <v>0.08064516129032258</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1451612903225807</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="D41" t="n">
         <v>7</v>
@@ -1815,13 +1815,13 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3021773225031483</v>
+        <v>0.2550223919490628</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1451612903225807</v>
+        <v>0.08064516129032258</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2236693064128645</v>
+        <v>0.1678337766196927</v>
       </c>
       <c r="I41" t="n">
         <v>0.5149786364148489</v>
@@ -1833,29 +1833,29 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>sec62</t>
+          <t>sec39</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.1129032258064516</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7580645161290323</v>
+        <v>0.5645161290322581</v>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2925541475357589</v>
+        <v>0.4475624814681164</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1129032258064516</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2027286866711053</v>
+        <v>0.4012005955727679</v>
       </c>
       <c r="I42" t="n">
         <v>0.5149786364148489</v>
@@ -1867,29 +1867,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>sec3</t>
+          <t>sec23</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.04838709677419355</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7903225806451613</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="D43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1955541234351958</v>
+        <v>0.4411223977799143</v>
       </c>
       <c r="G43" t="n">
-        <v>0.04838709677419355</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1219706101046947</v>
+        <v>0.3979805537286668</v>
       </c>
       <c r="I43" t="n">
         <v>0.5149786364148489</v>
@@ -1901,14 +1901,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>sec23</t>
+          <t>sec46</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.5645161290322581</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3709677419354839</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="D44" t="n">
         <v>8</v>
@@ -1917,13 +1917,13 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4510364985196633</v>
+        <v>0.4267340824297727</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3709677419354839</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="H44" t="n">
-        <v>0.4110021202275736</v>
+        <v>0.3746573637955315</v>
       </c>
       <c r="I44" t="n">
         <v>0.5149786364148489</v>
@@ -1935,14 +1935,14 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>sec39</t>
+          <t>sec60</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.3548387096774194</v>
+        <v>0.3064516129032258</v>
       </c>
       <c r="C45" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.6290322580645161</v>
       </c>
       <c r="D45" t="n">
         <v>8</v>
@@ -1951,13 +1951,13 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4411223977799143</v>
+        <v>0.4390534706069742</v>
       </c>
       <c r="G45" t="n">
-        <v>0.3548387096774194</v>
+        <v>0.3064516129032258</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3979805537286668</v>
+        <v>0.3727525417551</v>
       </c>
       <c r="I45" t="n">
         <v>0.5149786364148489</v>
@@ -1969,14 +1969,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>sec46</t>
+          <t>sec62</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5645161290322581</v>
+        <v>0.1129032258064516</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.7580645161290323</v>
       </c>
       <c r="D46" t="n">
         <v>8</v>
@@ -1985,13 +1985,13 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4267340824297727</v>
+        <v>0.2925541475357589</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.1129032258064516</v>
       </c>
       <c r="H46" t="n">
-        <v>0.3746573637955315</v>
+        <v>0.2027286866711053</v>
       </c>
       <c r="I46" t="n">
         <v>0.5149786364148489</v>
@@ -2003,14 +2003,14 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>sec60</t>
+          <t>sec3</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.3064516129032258</v>
+        <v>0.04838709677419355</v>
       </c>
       <c r="C47" t="n">
-        <v>0.6290322580645161</v>
+        <v>0.7903225806451613</v>
       </c>
       <c r="D47" t="n">
         <v>8</v>
@@ -2019,13 +2019,13 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4390534706069742</v>
+        <v>0.1955541234351958</v>
       </c>
       <c r="G47" t="n">
-        <v>0.3064516129032258</v>
+        <v>0.04838709677419355</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3727525417551</v>
+        <v>0.1219706101046947</v>
       </c>
       <c r="I47" t="n">
         <v>0.5149786364148489</v>
@@ -2037,29 +2037,29 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>sec58</t>
+          <t>sec22</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7258064516129032</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="D48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2163936752419151</v>
+        <v>0.3950789907714803</v>
       </c>
       <c r="G48" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1404549021370866</v>
+        <v>0.3588298179663854</v>
       </c>
       <c r="I48" t="n">
         <v>0.5149786364148489</v>
@@ -2071,14 +2071,14 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>sec22</t>
+          <t>sec11</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.532258064516129</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="D49" t="n">
         <v>9</v>
@@ -2087,13 +2087,13 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3950789907714803</v>
+        <v>0.3209636893892323</v>
       </c>
       <c r="G49" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="H49" t="n">
-        <v>0.3588298179663854</v>
+        <v>0.2572560382430032</v>
       </c>
       <c r="I49" t="n">
         <v>0.5149786364148489</v>
@@ -2105,14 +2105,14 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>sec54</t>
+          <t>sec40</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5161290322580645</v>
+        <v>0.3387096774193548</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1935483870967742</v>
+        <v>0.2096774193548387</v>
       </c>
       <c r="D50" t="n">
         <v>9</v>
@@ -2121,13 +2121,13 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3160631926171842</v>
+        <v>0.2664953490622307</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1935483870967742</v>
+        <v>0.2096774193548387</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2548057898569792</v>
+        <v>0.2380863842085347</v>
       </c>
       <c r="I50" t="n">
         <v>0.5149786364148489</v>
@@ -2139,14 +2139,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>sec11</t>
+          <t>sec12</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.532258064516129</v>
+        <v>0.09677419354838709</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1774193548387097</v>
+        <v>0.5806451612903226</v>
       </c>
       <c r="D51" t="n">
         <v>9</v>
@@ -2155,13 +2155,13 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0.3072993368267363</v>
+        <v>0.2370473944628882</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1774193548387097</v>
+        <v>0.09677419354838709</v>
       </c>
       <c r="H51" t="n">
-        <v>0.242359345832723</v>
+        <v>0.1669107940056376</v>
       </c>
       <c r="I51" t="n">
         <v>0.5149786364148489</v>
@@ -2173,14 +2173,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>sec40</t>
+          <t>sec58</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3387096774193548</v>
+        <v>0.06451612903225806</v>
       </c>
       <c r="C52" t="n">
-        <v>0.2096774193548387</v>
+        <v>0.7258064516129032</v>
       </c>
       <c r="D52" t="n">
         <v>9</v>
@@ -2189,13 +2189,13 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2664953490622307</v>
+        <v>0.2163936752419151</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2096774193548387</v>
+        <v>0.06451612903225806</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2380863842085347</v>
+        <v>0.1404549021370866</v>
       </c>
       <c r="I52" t="n">
         <v>0.5149786364148489</v>
@@ -2207,29 +2207,29 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>sec12</t>
+          <t>sec20</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.09677419354838709</v>
+        <v>0.2419354838709677</v>
       </c>
       <c r="C53" t="n">
-        <v>0.5806451612903226</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="D53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2370473944628882</v>
+        <v>0.2337318830030555</v>
       </c>
       <c r="G53" t="n">
-        <v>0.09677419354838709</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1669107940056376</v>
+        <v>0.2297691673079794</v>
       </c>
       <c r="I53" t="n">
         <v>0.5149786364148489</v>
@@ -2241,14 +2241,14 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>sec20</t>
+          <t>sec18</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.2419354838709677</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2419354838709677</v>
+        <v>0.1774193548387097</v>
       </c>
       <c r="D54" t="n">
         <v>10</v>
@@ -2257,13 +2257,13 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2419354838709677</v>
+        <v>0.2727666858917381</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2419354838709677</v>
+        <v>0.1774193548387097</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2419354838709677</v>
+        <v>0.2250930203652239</v>
       </c>
       <c r="I54" t="n">
         <v>0.5149786364148489</v>
@@ -2275,11 +2275,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>sec18</t>
+          <t>sec54</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4193548387096774</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="C55" t="n">
         <v>0.1612903225806452</v>
@@ -2291,13 +2291,13 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2600728305902758</v>
+        <v>0.2885249003225535</v>
       </c>
       <c r="G55" t="n">
         <v>0.1612903225806452</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2106815765854605</v>
+        <v>0.2249076114515993</v>
       </c>
       <c r="I55" t="n">
         <v>0.5149786364148489</v>
@@ -2316,7 +2316,7 @@
         <v>0.1612903225806452</v>
       </c>
       <c r="C56" t="n">
-        <v>0.2580645161290323</v>
+        <v>0.2419354838709677</v>
       </c>
       <c r="D56" t="n">
         <v>10</v>
@@ -2325,13 +2325,13 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2040179135592503</v>
+        <v>0.1975394953857402</v>
       </c>
       <c r="G56" t="n">
         <v>0.1612903225806452</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1826541180699477</v>
+        <v>0.1794149089831927</v>
       </c>
       <c r="I56" t="n">
         <v>0.5149786364148489</v>
@@ -2350,7 +2350,7 @@
         <v>0.1290322580645161</v>
       </c>
       <c r="C57" t="n">
-        <v>0.4193548387096774</v>
+        <v>0.4032258064516129</v>
       </c>
       <c r="D57" t="n">
         <v>10</v>
@@ -2359,13 +2359,13 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2326162113202574</v>
+        <v>0.2280989616730798</v>
       </c>
       <c r="G57" t="n">
         <v>0.1290322580645161</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1808242346923867</v>
+        <v>0.178565609868798</v>
       </c>
       <c r="I57" t="n">
         <v>0.5149786364148489</v>
@@ -2377,14 +2377,14 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>sec10</t>
+          <t>sec51</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1129032258064516</v>
+        <v>0.4354838709677419</v>
       </c>
       <c r="D58" t="n">
         <v>10</v>
@@ -2393,13 +2393,13 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.2375954816557457</v>
+        <v>0.1185236972314441</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1129032258064516</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1752493537310987</v>
+        <v>0.07539088087378656</v>
       </c>
       <c r="I58" t="n">
         <v>0.5149786364148489</v>
@@ -2411,29 +2411,29 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>sec51</t>
+          <t>sec10</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.5</v>
       </c>
       <c r="C59" t="n">
-        <v>0.4354838709677419</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="D59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1185236972314441</v>
+        <v>0.254000254000381</v>
       </c>
       <c r="G59" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="H59" t="n">
-        <v>0.07539088087378656</v>
+        <v>0.1915162560324486</v>
       </c>
       <c r="I59" t="n">
         <v>0.5149786364148489</v>
@@ -2445,14 +2445,14 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>sec56</t>
+          <t>sec55</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.1935483870967742</v>
+        <v>0.01612903225806452</v>
       </c>
       <c r="C60" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="D60" t="n">
         <v>11</v>
@@ -2461,13 +2461,13 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1580315963085921</v>
+        <v>0.06842968850192395</v>
       </c>
       <c r="G60" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.01612903225806452</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1435319271865541</v>
+        <v>0.04227936037999423</v>
       </c>
       <c r="I60" t="n">
         <v>0.5149786364148489</v>
@@ -2479,29 +2479,29 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>sec16</t>
+          <t>sec56</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4354838709677419</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="C61" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.1129032258064516</v>
       </c>
       <c r="D61" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1676178200873107</v>
+        <v>0.1478250224179303</v>
       </c>
       <c r="G61" t="n">
-        <v>0.06451612903225806</v>
+        <v>0.1129032258064516</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1160669745597844</v>
+        <v>0.1303641241121909</v>
       </c>
       <c r="I61" t="n">
         <v>0.5149786364148489</v>
@@ -2513,29 +2513,29 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>sec55</t>
+          <t>sec16</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.4354838709677419</v>
       </c>
       <c r="C62" t="n">
-        <v>0.2903225806451613</v>
+        <v>0.06451612903225806</v>
       </c>
       <c r="D62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0.06842968850192395</v>
+        <v>0.1676178200873107</v>
       </c>
       <c r="G62" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.06451612903225806</v>
       </c>
       <c r="H62" t="n">
-        <v>0.04227936037999423</v>
+        <v>0.1160669745597844</v>
       </c>
       <c r="I62" t="n">
         <v>0.5149786364148489</v>
@@ -2557,7 +2557,7 @@
         <v>0.09677419354838709</v>
       </c>
       <c r="D63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
@@ -2589,7 +2589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2609,7 +2609,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -2617,7 +2617,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2641,7 +2641,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -2665,7 +2665,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -2689,7 +2689,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -2697,6 +2697,14 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
         <v>1</v>
       </c>
     </row>
